--- a/Circuit Boards/BOM.xlsx
+++ b/Circuit Boards/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dylan\Documents\GitHub\Black_Body\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dylan\Documents\GitHub\Black_Body\Circuit Boards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322A330E-9AAA-47CF-A687-FF505AAD6F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1BE918-347B-4C70-BF9D-B1789E3B09FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="218" yWindow="900" windowWidth="21164" windowHeight="11662" xr2:uid="{8C143804-AE48-4691-8BB0-48B634FFE371}"/>
   </bookViews>
@@ -39,28 +39,688 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Part</t>
-  </si>
-  <si>
-    <t>Min Quantity</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="225">
   <si>
     <t>Heater</t>
   </si>
   <si>
     <t>TBH25P10R0JE</t>
+  </si>
+  <si>
+    <t>Designator</t>
+  </si>
+  <si>
+    <t>Footprint</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>LCSC Part #</t>
+  </si>
+  <si>
+    <t>C201, C202, C203, C204, C205, C206, C207, C208, C209, C210, C211, C212, C213, C214, C215, C216, C301, C302, C303, C304, C305, C306, C307, C308, C401, C402, C403, C404, C405, C406, C407, C408, C409, C410, C411, C412, C413, C414, C415, C416, C417, C418, C419, C420, C421, C422, C423, C424</t>
+  </si>
+  <si>
+    <t>0402</t>
+  </si>
+  <si>
+    <t>2u2</t>
+  </si>
+  <si>
+    <t>GRM155R61E225ME15D</t>
+  </si>
+  <si>
+    <t>C309</t>
+  </si>
+  <si>
+    <t>0603</t>
+  </si>
+  <si>
+    <t>200pf</t>
+  </si>
+  <si>
+    <t>CL10C201JB8NNNC</t>
+  </si>
+  <si>
+    <t>C501</t>
+  </si>
+  <si>
+    <t>220nf</t>
+  </si>
+  <si>
+    <t>GCM188R71H224KA64D</t>
+  </si>
+  <si>
+    <t>C502, C503, C504, C505, C506, C507, C508, C509, C510, C511, C512, C513, C514, C515, C516, C517, C518, C519, C701, C702, C704, C706, C707, C708, C709, C710, C711, C713, C714</t>
+  </si>
+  <si>
+    <t>0.1uf</t>
+  </si>
+  <si>
+    <t>CL10B104KB8NNNC</t>
+  </si>
+  <si>
+    <t>C601, C602, C606, C607, C609, C614, C615, C712</t>
+  </si>
+  <si>
+    <t>10uf</t>
+  </si>
+  <si>
+    <t>GRM188R6YA106MA73D</t>
+  </si>
+  <si>
+    <t>C603</t>
+  </si>
+  <si>
+    <t>1uf</t>
+  </si>
+  <si>
+    <t>C0603C105K4RACTU</t>
+  </si>
+  <si>
+    <t>C604, C605</t>
+  </si>
+  <si>
+    <t>10nf</t>
+  </si>
+  <si>
+    <t>CL10B103KB8NNNC</t>
+  </si>
+  <si>
+    <t>C608, C610, C611, C612, C613</t>
+  </si>
+  <si>
+    <t>4.7uf</t>
+  </si>
+  <si>
+    <t>CL10A475KO8NNNC</t>
+  </si>
+  <si>
+    <t>C703, C705</t>
+  </si>
+  <si>
+    <t>28pf</t>
+  </si>
+  <si>
+    <t>CL10C270JB8NNNC</t>
+  </si>
+  <si>
+    <t>C715</t>
+  </si>
+  <si>
+    <t>22uf</t>
+  </si>
+  <si>
+    <t>CL10A226MP8NUNE</t>
+  </si>
+  <si>
+    <t>D201</t>
+  </si>
+  <si>
+    <t>D_DO-35_SOD27_P7.62mm_Horizontal</t>
+  </si>
+  <si>
+    <t>1N457</t>
+  </si>
+  <si>
+    <t>D301</t>
+  </si>
+  <si>
+    <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+  </si>
+  <si>
+    <t>LT1004-1.2</t>
+  </si>
+  <si>
+    <t>D601</t>
+  </si>
+  <si>
+    <t>D_SMA</t>
+  </si>
+  <si>
+    <t>SMAJ24A</t>
+  </si>
+  <si>
+    <t>D701</t>
+  </si>
+  <si>
+    <t>D_SOD-323</t>
+  </si>
+  <si>
+    <t>1N5819WS</t>
+  </si>
+  <si>
+    <t>J401, J402</t>
+  </si>
+  <si>
+    <t>CUI_TB002-500-02BE</t>
+  </si>
+  <si>
+    <t>Screw_Terminal_01x02</t>
+  </si>
+  <si>
+    <t>TB002-500-02BE</t>
+  </si>
+  <si>
+    <t>J702</t>
+  </si>
+  <si>
+    <t>CONN_5040500891_MOL</t>
+  </si>
+  <si>
+    <t>J703</t>
+  </si>
+  <si>
+    <t>UJ20-C-H-G-SMT-1-P16-TR</t>
+  </si>
+  <si>
+    <t>USB_C_Receptacle_USB2.0_16P</t>
+  </si>
+  <si>
+    <t>P601</t>
+  </si>
+  <si>
+    <t>436500200 2-pin</t>
+  </si>
+  <si>
+    <t>Q201, Q202, Q301, Q401, Q402, Q403</t>
+  </si>
+  <si>
+    <t>TSSOP-16_4.4x5mm_P0.65mm</t>
+  </si>
+  <si>
+    <t>TMUX1112PWR</t>
+  </si>
+  <si>
+    <t>R201, R202, R203, R204, R205, R206, R207, R208, R301, R302, R303, R304, R401, R402, R403, R404, R408, R409, R410, R411, R414, R415, R416, R417, R701, R702</t>
+  </si>
+  <si>
+    <t>5.1k</t>
+  </si>
+  <si>
+    <t>RT0402BRD075K1L</t>
+  </si>
+  <si>
+    <t>R209</t>
+  </si>
+  <si>
+    <t>RQ73C1J133RBTD</t>
+  </si>
+  <si>
+    <t>R210, R211</t>
+  </si>
+  <si>
+    <t>1.33k</t>
+  </si>
+  <si>
+    <t>ERA-3AEB1331V</t>
+  </si>
+  <si>
+    <t>R212, R213</t>
+  </si>
+  <si>
+    <t>13.3k</t>
+  </si>
+  <si>
+    <t>ERA-3AEB1332V</t>
+  </si>
+  <si>
+    <t>R214, R215</t>
+  </si>
+  <si>
+    <t>134k</t>
+  </si>
+  <si>
+    <t>ERA-3AEB1333V</t>
+  </si>
+  <si>
+    <t>R216</t>
+  </si>
+  <si>
+    <t>1.33M</t>
+  </si>
+  <si>
+    <t>RK73H1JTTD1334F</t>
+  </si>
+  <si>
+    <t>R305, R502, R504</t>
+  </si>
+  <si>
+    <t>10M</t>
+  </si>
+  <si>
+    <t>CRCW060310M0DHEAP</t>
+  </si>
+  <si>
+    <t>R306</t>
+  </si>
+  <si>
+    <t>22.6k</t>
+  </si>
+  <si>
+    <t>ERA-3AEB2262V</t>
+  </si>
+  <si>
+    <t>R307</t>
+  </si>
+  <si>
+    <t>100k</t>
+  </si>
+  <si>
+    <t>ERA-3AEB104V</t>
+  </si>
+  <si>
+    <t>R308</t>
+  </si>
+  <si>
+    <t>100M</t>
+  </si>
+  <si>
+    <t>HVC0603T1006FET</t>
+  </si>
+  <si>
+    <t>R309</t>
+  </si>
+  <si>
+    <t>226k</t>
+  </si>
+  <si>
+    <t>ERA-3AEB2263V</t>
+  </si>
+  <si>
+    <t>R310</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>RN73H1JTTD1004B25</t>
+  </si>
+  <si>
+    <t>R311</t>
+  </si>
+  <si>
+    <t>2.7k</t>
+  </si>
+  <si>
+    <t>ERA-3AEB272V</t>
+  </si>
+  <si>
+    <t>R405</t>
+  </si>
+  <si>
+    <t>RN73C1J4R99BTD</t>
+  </si>
+  <si>
+    <t>R406, R606, R616</t>
+  </si>
+  <si>
+    <t>ERA-3AEB4990V</t>
+  </si>
+  <si>
+    <t>R407, R605, R608</t>
+  </si>
+  <si>
+    <t>33.2k</t>
+  </si>
+  <si>
+    <t>ERA-3AEB3322V</t>
+  </si>
+  <si>
+    <t>R412, R413, R505, R506, R703, R704</t>
+  </si>
+  <si>
+    <t>10k</t>
+  </si>
+  <si>
+    <t>ERA-3AEB103V</t>
+  </si>
+  <si>
+    <t>R501, R503</t>
+  </si>
+  <si>
+    <t>ERA-3AEB49R9V</t>
+  </si>
+  <si>
+    <t>R601, R604</t>
+  </si>
+  <si>
+    <t>569k</t>
+  </si>
+  <si>
+    <t>RN73H1JTTD5693B50</t>
+  </si>
+  <si>
+    <t>R602, R603, R607, R609</t>
+  </si>
+  <si>
+    <t>180k</t>
+  </si>
+  <si>
+    <t>ERA-3AEB184V</t>
+  </si>
+  <si>
+    <t>R610</t>
+  </si>
+  <si>
+    <t>7.5k</t>
+  </si>
+  <si>
+    <t>ERA-3AEB752V</t>
+  </si>
+  <si>
+    <t>R611, R613</t>
+  </si>
+  <si>
+    <t>448k</t>
+  </si>
+  <si>
+    <t>RT0603BRD07448KL</t>
+  </si>
+  <si>
+    <t>R612, R614</t>
+  </si>
+  <si>
+    <t>50k</t>
+  </si>
+  <si>
+    <t>RT0603BRD0750KL</t>
+  </si>
+  <si>
+    <t>SW701, SW702</t>
+  </si>
+  <si>
+    <t>SW_MEC_5E</t>
+  </si>
+  <si>
+    <t>U201, U301</t>
+  </si>
+  <si>
+    <t>LM334M</t>
+  </si>
+  <si>
+    <t>U302</t>
+  </si>
+  <si>
+    <t>LT1008</t>
+  </si>
+  <si>
+    <t>U501, U502, U503, U504, U509</t>
+  </si>
+  <si>
+    <t>SOT-23-5</t>
+  </si>
+  <si>
+    <t>OPA376xxDBV</t>
+  </si>
+  <si>
+    <t>OPA376AIDBVR</t>
+  </si>
+  <si>
+    <t>U505, U506</t>
+  </si>
+  <si>
+    <t>AD8421ARZ</t>
+  </si>
+  <si>
+    <t>U507</t>
+  </si>
+  <si>
+    <t>TSSOP-20_4.4x6.5mm_P0.65mm</t>
+  </si>
+  <si>
+    <t>ADS131M04xPW</t>
+  </si>
+  <si>
+    <t>ADS131M04IPWR</t>
+  </si>
+  <si>
+    <t>U508</t>
+  </si>
+  <si>
+    <t>SSOP-16_3.9x4.9mm_P0.635mm</t>
+  </si>
+  <si>
+    <t>ISO7762FDBQ</t>
+  </si>
+  <si>
+    <t>U601</t>
+  </si>
+  <si>
+    <t>MSOP-16-1EP_3x4.039mm_P0.5mm_EP1.651x2.845mm</t>
+  </si>
+  <si>
+    <t>LTC3260xMSE</t>
+  </si>
+  <si>
+    <t>LTC3260EMSE#TRPBF</t>
+  </si>
+  <si>
+    <t>U602</t>
+  </si>
+  <si>
+    <t>MSOP-12-1EP_3x4.039mm_P0.65mm_EP1.651x2.845mm</t>
+  </si>
+  <si>
+    <t>LT3094xMSE</t>
+  </si>
+  <si>
+    <t>LT3094EMSE#TRPBF</t>
+  </si>
+  <si>
+    <t>U603</t>
+  </si>
+  <si>
+    <t>MSOP-10-1EP_3x3mm_P0.5mm_EP1.68x1.88mm</t>
+  </si>
+  <si>
+    <t>LT3042xMSE</t>
+  </si>
+  <si>
+    <t>LT3042EMSE#TRPBF</t>
+  </si>
+  <si>
+    <t>U701</t>
+  </si>
+  <si>
+    <t>TSSOP-14_4.4x5mm_P0.65mm</t>
+  </si>
+  <si>
+    <t>TXU0304</t>
+  </si>
+  <si>
+    <t>U702</t>
+  </si>
+  <si>
+    <t>ABM8G-25.000MHZ-18-D2Y-T</t>
+  </si>
+  <si>
+    <t>U703</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>USBLC6-2SC6</t>
+  </si>
+  <si>
+    <t>USBLC6-2SC6c</t>
+  </si>
+  <si>
+    <t>U704</t>
+  </si>
+  <si>
+    <t>LQFP-64_10x10mm_P0.5mm</t>
+  </si>
+  <si>
+    <t>STM32G431RBTx</t>
+  </si>
+  <si>
+    <t>STM32G431RBT6</t>
+  </si>
+  <si>
+    <t>U705</t>
+  </si>
+  <si>
+    <t>SOT-223-3_TabPin2</t>
+  </si>
+  <si>
+    <t>AMS1117-3.3</t>
+  </si>
+  <si>
+    <t>430471035826</t>
+  </si>
+  <si>
+    <t>Mating pwr</t>
+  </si>
+  <si>
+    <t>Mating signal</t>
+  </si>
+  <si>
+    <t>C201, C307, C308, C309</t>
+  </si>
+  <si>
+    <t>C202, C204, C207, C301, C305, C306, C310, C311, C312</t>
+  </si>
+  <si>
+    <t>100nf</t>
+  </si>
+  <si>
+    <t>C203, C206</t>
+  </si>
+  <si>
+    <t>C205, C302, C303, C304</t>
+  </si>
+  <si>
+    <t>RED</t>
+  </si>
+  <si>
+    <t>LTST-C191KRKT</t>
+  </si>
+  <si>
+    <t>D202</t>
+  </si>
+  <si>
+    <t>J201</t>
+  </si>
+  <si>
+    <t>J203</t>
+  </si>
+  <si>
+    <t>L301</t>
+  </si>
+  <si>
+    <t>SRR1208</t>
+  </si>
+  <si>
+    <t>SRR1208-120ML</t>
+  </si>
+  <si>
+    <t>P301, P302</t>
+  </si>
+  <si>
+    <t>Q302</t>
+  </si>
+  <si>
+    <t>TO-126-3_Vertical</t>
+  </si>
+  <si>
+    <t>BD139</t>
+  </si>
+  <si>
+    <t>R201, R203, R204, R205, R308</t>
+  </si>
+  <si>
+    <t>R202, R302</t>
+  </si>
+  <si>
+    <t>R206, R207, R303, R311</t>
+  </si>
+  <si>
+    <t>R301</t>
+  </si>
+  <si>
+    <t>0805</t>
+  </si>
+  <si>
+    <t>100m</t>
+  </si>
+  <si>
+    <t>RCWE0805R100FKEA</t>
+  </si>
+  <si>
+    <t>R304, R305</t>
+  </si>
+  <si>
+    <t>CRM2512-FX-5R10ELF</t>
+  </si>
+  <si>
+    <t>162k</t>
+  </si>
+  <si>
+    <t>CRCW0603162KFKEA</t>
+  </si>
+  <si>
+    <t>SW201, SW202</t>
+  </si>
+  <si>
+    <t>U201</t>
+  </si>
+  <si>
+    <t>U202</t>
+  </si>
+  <si>
+    <t>ESP32-S3-WROOM-1</t>
+  </si>
+  <si>
+    <t>ESP32-S3-WROOM-1-N8R8</t>
+  </si>
+  <si>
+    <t>U203</t>
+  </si>
+  <si>
+    <t>U301</t>
+  </si>
+  <si>
+    <t>TSSOP-10_3x3mm_P0.5mm</t>
+  </si>
+  <si>
+    <t>DAC60501ZDGSR</t>
+  </si>
+  <si>
+    <t>INA181A2IDBVR</t>
+  </si>
+  <si>
+    <t>U303</t>
+  </si>
+  <si>
+    <t>TLV9061xDBV</t>
+  </si>
+  <si>
+    <t>U304</t>
+  </si>
+  <si>
+    <t>LMR51420XFDDCR</t>
+  </si>
+  <si>
+    <t>LT1008S8#PBF</t>
+  </si>
+  <si>
+    <t>LT1004CS8-1.2#TRPBF</t>
+  </si>
+  <si>
+    <t>LM358BAIDR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,13 +736,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -98,15 +778,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -120,9 +837,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -160,7 +877,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -266,7 +983,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -408,7 +1125,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -416,39 +1133,1511 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1CC7221-E739-4684-BFB9-A32AA078EB56}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="12.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.73046875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3">
+        <v>48</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>5040500891</v>
+      </c>
+      <c r="E17" s="7">
+        <v>5040500891</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
+        <v>436500200</v>
+      </c>
+      <c r="E19" s="6">
+        <v>436500200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="3">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="3">
+        <v>26</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>133</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="3">
+        <v>3</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A29" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A31" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A32" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="3">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3">
+        <v>4.99</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="3">
+        <v>3</v>
+      </c>
+      <c r="D35" s="3">
+        <v>500</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="3">
+        <v>3</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A37" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="3">
+        <v>6</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="3">
+        <v>2</v>
+      </c>
+      <c r="D38" s="3">
+        <v>50</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="3">
+        <v>2</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="3">
+        <v>4</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="3">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="3">
+        <v>2</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A43" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="3">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A44" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="3">
+        <v>430471035826</v>
+      </c>
+      <c r="C44" s="3">
+        <v>2</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="3">
+        <v>2</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="3">
+        <v>5</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="3">
+        <v>2</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A49" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" s="3">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A50" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C50" s="3">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A51" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" s="3">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A52" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" s="3">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A53" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" s="3">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A54" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A55" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C55" s="3">
+        <v>1</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A56" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A57" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A58" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="C60">
+        <v>4</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>178</v>
+      </c>
+      <c r="C61">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>179</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>180</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="D65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>181</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66">
+        <v>9</v>
+      </c>
+      <c r="D66" t="s">
+        <v>182</v>
+      </c>
+      <c r="E66" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>183</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="D67" t="s">
+        <v>37</v>
+      </c>
+      <c r="E67" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>184</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68">
         <v>4</v>
+      </c>
+      <c r="D68" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69" t="s">
+        <v>185</v>
+      </c>
+      <c r="E69" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>187</v>
+      </c>
+      <c r="B70" t="s">
+        <v>49</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70" t="s">
+        <v>50</v>
+      </c>
+      <c r="E70" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>188</v>
+      </c>
+      <c r="B71" t="s">
+        <v>56</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71" s="3">
+        <v>5040500891</v>
+      </c>
+      <c r="E71" s="3">
+        <v>5040500891</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72" t="s">
+        <v>59</v>
+      </c>
+      <c r="E72" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>190</v>
+      </c>
+      <c r="B73" t="s">
+        <v>191</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73" t="s">
+        <v>192</v>
+      </c>
+      <c r="E73" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>193</v>
+      </c>
+      <c r="B74" t="s">
+        <v>61</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="D74" s="3">
+        <v>436500200</v>
+      </c>
+      <c r="E74" s="3">
+        <v>436500200</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>194</v>
+      </c>
+      <c r="B75" t="s">
+        <v>195</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75" t="s">
+        <v>196</v>
+      </c>
+      <c r="E75" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>197</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76">
+        <v>5</v>
+      </c>
+      <c r="D76" t="s">
+        <v>111</v>
+      </c>
+      <c r="E76" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>198</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77" t="s">
+        <v>71</v>
+      </c>
+      <c r="E77" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>199</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78">
+        <v>4</v>
+      </c>
+      <c r="D78" t="s">
+        <v>66</v>
+      </c>
+      <c r="E78" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>200</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79" t="s">
+        <v>202</v>
+      </c>
+      <c r="E79" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>204</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80" s="3">
+        <v>500</v>
+      </c>
+      <c r="E80" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" s="3">
+        <v>2512</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E81" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="s">
+        <v>89</v>
+      </c>
+      <c r="E82" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>94</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83" t="s">
+        <v>206</v>
+      </c>
+      <c r="E83" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>97</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84" t="s">
+        <v>86</v>
+      </c>
+      <c r="E84" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>208</v>
+      </c>
+      <c r="B85">
+        <v>430471035826</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+      <c r="D85" t="s">
+        <v>131</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>209</v>
+      </c>
+      <c r="B86" t="s">
+        <v>175</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86" t="s">
+        <v>176</v>
+      </c>
+      <c r="E86" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>210</v>
+      </c>
+      <c r="B87" t="s">
+        <v>211</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87" t="s">
+        <v>212</v>
+      </c>
+      <c r="E87" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>213</v>
+      </c>
+      <c r="B88" t="s">
+        <v>167</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88" t="s">
+        <v>168</v>
+      </c>
+      <c r="E88" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>214</v>
+      </c>
+      <c r="B89" t="s">
+        <v>215</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89" t="s">
+        <v>216</v>
+      </c>
+      <c r="E89" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>134</v>
+      </c>
+      <c r="B90" t="s">
+        <v>167</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90" t="s">
+        <v>217</v>
+      </c>
+      <c r="E90" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>218</v>
+      </c>
+      <c r="B91" t="s">
+        <v>137</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91" t="s">
+        <v>219</v>
+      </c>
+      <c r="E91" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>220</v>
+      </c>
+      <c r="B92" t="s">
+        <v>167</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="s">
+        <v>221</v>
+      </c>
+      <c r="E92" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{9DE3EE78-1E26-41A3-B34A-5FF495F1858A}"/>
+    <hyperlink ref="E60" r:id="rId1" xr:uid="{4A5C600B-BE73-46C1-9943-538822EF3F64}"/>
+    <hyperlink ref="D60" r:id="rId2" xr:uid="{B7B14ED3-A957-4E3D-864C-8EE8CF7A8F39}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Circuit Boards/BOM.xlsx
+++ b/Circuit Boards/BOM.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1BE918-347B-4C70-BF9D-B1789E3B09FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="218" yWindow="900" windowWidth="21164" windowHeight="11662" xr2:uid="{8C143804-AE48-4691-8BB0-48B634FFE371}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{8C143804-AE48-4691-8BB0-48B634FFE371}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -802,28 +802,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
